--- a/outputs/daily/hr_rankings_2026-08-13_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-13_remaining.xlsx
@@ -1106,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1390,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1674,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1958,34 +1946,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2240,28 +2224,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2518,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2802,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3086,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3368,28 +3344,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3646,34 +3626,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3930,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4494,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4778,34 +4746,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5342,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5906,34 +5866,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6190,34 +6146,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6474,34 +6426,30 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6758,34 +6706,30 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7322,34 +7266,30 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8446,34 +8386,30 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8730,34 +8666,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9014,34 +8946,30 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9296,28 +9224,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9574,34 +9506,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9856,28 +9784,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10132,28 +10064,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10410,34 +10346,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11580,34 +11512,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11864,34 +11792,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12148,34 +12072,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12432,34 +12352,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12714,28 +12630,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12992,34 +12912,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -13276,34 +13192,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -13560,34 +13472,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13842,28 +13750,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14120,34 +14032,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14404,34 +14312,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -14968,34 +14872,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15252,34 +15152,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15816,34 +15712,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -16380,34 +16272,30 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16664,34 +16552,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
